--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2026\project\self-order-remake\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rian\self-order-backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CCF3D8F-1E89-4896-8EB4-3F2AED69C896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9626E2DA-1E6E-484D-A821-93424B88331E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3620B830-7B27-4AF4-B766-B2E83C0C6CDE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3620B830-7B27-4AF4-B766-B2E83C0C6CDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,16 +27,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>Method</t>
   </si>
@@ -93,13 +94,34 @@
   </si>
   <si>
     <t>Show the details of a specific produk</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>/v1/grupproduk</t>
+  </si>
+  <si>
+    <t>grup produk</t>
+  </si>
+  <si>
+    <t>createGrupProdukHandler</t>
+  </si>
+  <si>
+    <t>Create a new grup produk</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -464,16 +486,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B31B2B8-7DC6-4B90-8975-DA41F3A24C95}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" customWidth="1"/>
-    <col min="4" max="4" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.125" customWidth="1"/>
+    <col min="4" max="4" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -489,8 +511,11 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -506,39 +531,68 @@
       <c r="E2" t="s">
         <v>8</v>
       </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E5" t="s">
         <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rian\self-order-backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9626E2DA-1E6E-484D-A821-93424B88331E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5A62B8-49AE-4BEB-B902-21CBA07EEAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3620B830-7B27-4AF4-B766-B2E83C0C6CDE}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
   <si>
     <t>Method</t>
   </si>
@@ -66,9 +66,6 @@
     <t>Show application information</t>
   </si>
   <si>
-    <t xml:space="preserve"> GET</t>
-  </si>
-  <si>
     <t>Root</t>
   </si>
   <si>
@@ -115,6 +112,36 @@
   </si>
   <si>
     <t>Create a new grup produk</t>
+  </si>
+  <si>
+    <t>Implemented</t>
+  </si>
+  <si>
+    <t>Secured</t>
+  </si>
+  <si>
+    <t>updateProdukHandler</t>
+  </si>
+  <si>
+    <t>Update the details of a specific produk</t>
+  </si>
+  <si>
+    <t>deleteProdukHandler</t>
+  </si>
+  <si>
+    <t>Delete a specific produk</t>
+  </si>
+  <si>
+    <t>PUT</t>
+  </si>
+  <si>
+    <t>DELETE</t>
+  </si>
+  <si>
+    <t>listProdukHandler</t>
+  </si>
+  <si>
+    <t>Show the details of all produk</t>
   </si>
 </sst>
 </file>
@@ -486,16 +513,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B31B2B8-7DC6-4B90-8975-DA41F3A24C95}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.875" customWidth="1"/>
     <col min="3" max="3" width="14.125" customWidth="1"/>
     <col min="4" max="4" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.125" customWidth="1"/>
+    <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -503,7 +532,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -512,10 +541,16 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="G1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -523,7 +558,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -532,67 +567,169 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E5" t="s">
         <v>17</v>
       </c>
-      <c r="F4" t="s">
-        <v>21</v>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
